--- a/data/trans_orig/P36B04-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P36B04-Estudios-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la frecuencia de consumo de legumbres en 2007</t>
+          <t>Población según la frecuencia de consumo de legumbres en 2007 (tasa de respuesta: 99,94%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6251</t>
+          <t>5700</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>22391</t>
+          <t>21274</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>9681</t>
+          <t>9712</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>27869</t>
+          <t>27147</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -787,7 +787,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>18482</t>
+          <t>18156</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>40956</t>
+          <t>42617</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,82%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>71481</t>
+          <t>71162</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>105512</t>
+          <t>106000</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>6,9%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>10,24%</t>
+          <t>10,28%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>83356</t>
+          <t>84123</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>121982</t>
+          <t>122467</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>9,28%</t>
+          <t>9,31%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>163417</t>
+          <t>162878</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>217803</t>
+          <t>217616</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>6,94%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>552791</t>
+          <t>555187</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>613158</t>
+          <t>615187</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>53,63%</t>
+          <t>53,86%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>59,48%</t>
+          <t>59,68%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>759583</t>
+          <t>754887</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>830645</t>
+          <t>828853</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>57,76%</t>
+          <t>57,4%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>63,16%</t>
+          <t>63,03%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1327062</t>
+          <t>1328846</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1424769</t>
+          <t>1424190</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>56,57%</t>
+          <t>56,64%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>60,73%</t>
+          <t>60,71%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>300393</t>
+          <t>297647</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>357618</t>
+          <t>355456</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>29,14%</t>
+          <t>28,87%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>34,69%</t>
+          <t>34,48%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>348891</t>
+          <t>347980</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>414836</t>
+          <t>414016</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>26,53%</t>
+          <t>26,46%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>31,54%</t>
+          <t>31,48%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>667167</t>
+          <t>666805</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>756048</t>
+          <t>751638</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>28,44%</t>
+          <t>28,42%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>32,23%</t>
+          <t>32,04%</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>10741</t>
+          <t>10906</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>27854</t>
+          <t>27643</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1219,12 +1219,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>14302</t>
+          <t>13953</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>32879</t>
+          <t>32651</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1234,12 +1234,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>28519</t>
+          <t>29386</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>53612</t>
+          <t>53483</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1269,12 +1269,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,28%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>11604</t>
+          <t>11430</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>30228</t>
+          <t>28747</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>14245</t>
+          <t>14181</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>32980</t>
+          <t>33402</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,7 +1469,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>29486</t>
+          <t>29998</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>56733</t>
+          <t>54156</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,65%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>211081</t>
+          <t>209235</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>266810</t>
+          <t>265645</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>12,46%</t>
+          <t>12,36%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>15,76%</t>
+          <t>15,69%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>134092</t>
+          <t>133006</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>180187</t>
+          <t>178498</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>8,39%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>11,37%</t>
+          <t>11,27%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>358710</t>
+          <t>356605</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>428183</t>
+          <t>429221</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>10,94%</t>
+          <t>10,88%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>13,06%</t>
+          <t>13,09%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>971351</t>
+          <t>970751</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1048678</t>
+          <t>1046249</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>57,36%</t>
+          <t>57,33%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>61,93%</t>
+          <t>61,78%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>962077</t>
+          <t>963788</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>1038500</t>
+          <t>1038330</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>60,72%</t>
+          <t>60,83%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>65,54%</t>
+          <t>65,53%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1947957</t>
+          <t>1960725</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>2064636</t>
+          <t>2072641</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>59,43%</t>
+          <t>59,82%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>62,99%</t>
+          <t>63,23%</t>
         </is>
       </c>
     </row>
@@ -1753,12 +1753,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>369954</t>
+          <t>370640</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>441836</t>
+          <t>439531</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1768,12 +1768,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>21,85%</t>
+          <t>21,89%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>26,09%</t>
+          <t>25,96%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1788,12 +1788,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>348022</t>
+          <t>352971</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>418254</t>
+          <t>422258</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1803,12 +1803,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>21,96%</t>
+          <t>22,28%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>26,4%</t>
+          <t>26,65%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>736001</t>
+          <t>742963</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>838515</t>
+          <t>836587</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>22,45%</t>
+          <t>22,67%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>25,58%</t>
+          <t>25,52%</t>
         </is>
       </c>
     </row>
@@ -1866,12 +1866,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>14908</t>
+          <t>15188</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>35363</t>
+          <t>34882</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1901,12 +1901,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>11709</t>
+          <t>11874</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>30098</t>
+          <t>31074</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1916,12 +1916,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>30641</t>
+          <t>31398</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>58917</t>
+          <t>57351</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1951,12 +1951,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,75%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3644</t>
+          <t>3269</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>15410</t>
+          <t>14622</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>4209</t>
+          <t>4113</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>16099</t>
+          <t>16893</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>9571</t>
+          <t>9244</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>25800</t>
+          <t>25633</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,49%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>77204</t>
+          <t>75808</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>112818</t>
+          <t>111374</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>14,0%</t>
+          <t>13,75%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>20,46%</t>
+          <t>20,2%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>31425</t>
+          <t>32846</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>56573</t>
+          <t>59841</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>6,89%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>11,87%</t>
+          <t>12,56%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>115493</t>
+          <t>114663</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>160628</t>
+          <t>162013</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>11,24%</t>
+          <t>11,16%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>15,63%</t>
+          <t>15,76%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>317191</t>
+          <t>320496</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>364058</t>
+          <t>367509</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>57,52%</t>
+          <t>58,12%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>66,02%</t>
+          <t>66,65%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>298333</t>
+          <t>296268</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>339216</t>
+          <t>339948</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>62,62%</t>
+          <t>62,19%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>71,2%</t>
+          <t>71,36%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>629551</t>
+          <t>633089</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>691764</t>
+          <t>695813</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>61,25%</t>
+          <t>61,6%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>67,3%</t>
+          <t>67,7%</t>
         </is>
       </c>
     </row>
@@ -2435,12 +2435,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>83549</t>
+          <t>83822</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>121646</t>
+          <t>121453</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2450,12 +2450,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>15,15%</t>
+          <t>15,2%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>22,06%</t>
+          <t>22,03%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2470,12 +2470,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>80795</t>
+          <t>80425</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>116615</t>
+          <t>116872</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2485,12 +2485,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>16,96%</t>
+          <t>16,88%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>24,48%</t>
+          <t>24,53%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>175083</t>
+          <t>176195</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>228552</t>
+          <t>228149</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>17,03%</t>
+          <t>17,14%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>22,24%</t>
+          <t>22,2%</t>
         </is>
       </c>
     </row>
@@ -2548,12 +2548,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2277</t>
+          <t>2299</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>15469</t>
+          <t>14703</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2583,12 +2583,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>2817</t>
+          <t>2129</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>13286</t>
+          <t>12205</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2598,12 +2598,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>6466</t>
+          <t>6419</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>21400</t>
+          <t>21425</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2633,7 +2633,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>26967</t>
+          <t>25992</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>52532</t>
+          <t>51886</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>34543</t>
+          <t>34629</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>62991</t>
+          <t>63120</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,7 +2828,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>67997</t>
+          <t>69288</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>108507</t>
+          <t>105400</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,58%</t>
         </is>
       </c>
     </row>
@@ -2891,12 +2891,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>377507</t>
+          <t>376843</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>450401</t>
+          <t>453484</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2906,12 +2906,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>11,52%</t>
+          <t>11,5%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>13,75%</t>
+          <t>13,84%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>267929</t>
+          <t>266845</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>339252</t>
+          <t>332759</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2941,12 +2941,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>7,9%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>10,05%</t>
+          <t>9,86%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>666264</t>
+          <t>664443</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>767694</t>
+          <t>772591</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>10,02%</t>
+          <t>9,99%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>11,54%</t>
+          <t>11,62%</t>
         </is>
       </c>
     </row>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1883691</t>
+          <t>1880651</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>1991651</t>
+          <t>1999380</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3019,12 +3019,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>57,51%</t>
+          <t>57,41%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>60,8%</t>
+          <t>61,04%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>2053999</t>
+          <t>2060570</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>2171994</t>
+          <t>2170249</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3054,12 +3054,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>60,84%</t>
+          <t>61,04%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>64,34%</t>
+          <t>64,29%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>3972286</t>
+          <t>3977594</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>4130786</t>
+          <t>4137982</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>59,72%</t>
+          <t>59,8%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>62,1%</t>
+          <t>62,21%</t>
         </is>
       </c>
     </row>
@@ -3117,12 +3117,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>789136</t>
+          <t>790027</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>883569</t>
+          <t>890315</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>24,09%</t>
+          <t>24,12%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>26,97%</t>
+          <t>27,18%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3152,12 +3152,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>815609</t>
+          <t>813721</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>919337</t>
+          <t>915619</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>24,16%</t>
+          <t>24,1%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>27,23%</t>
+          <t>27,12%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1629731</t>
+          <t>1627085</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1770494</t>
+          <t>1771672</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>24,5%</t>
+          <t>24,46%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>26,62%</t>
+          <t>26,64%</t>
         </is>
       </c>
     </row>
@@ -3230,12 +3230,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>35794</t>
+          <t>35391</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>64115</t>
+          <t>61438</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3245,12 +3245,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3265,12 +3265,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>34751</t>
+          <t>34894</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>64093</t>
+          <t>62499</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3285,7 +3285,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3300,12 +3300,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>77059</t>
+          <t>77619</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>115763</t>
+          <t>115112</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,73%</t>
         </is>
       </c>
     </row>
@@ -3496,7 +3496,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la frecuencia de consumo de legumbres en 2012</t>
+          <t>Población según la frecuencia de consumo de legumbres en 2012 (tasa de respuesta: 99,69%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3691,12 +3691,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6812</t>
+          <t>6511</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>22165</t>
+          <t>20854</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3706,12 +3706,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>6799</t>
+          <t>6552</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>21986</t>
+          <t>22778</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3741,12 +3741,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>15230</t>
+          <t>15917</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>37622</t>
+          <t>37534</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -3804,12 +3804,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>54256</t>
+          <t>53664</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>87946</t>
+          <t>86736</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3819,12 +3819,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>5,52%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>9,05%</t>
+          <t>8,93%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>65398</t>
+          <t>64850</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>102126</t>
+          <t>100107</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3854,12 +3854,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>7,51%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>128335</t>
+          <t>127308</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>176678</t>
+          <t>176660</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3889,7 +3889,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,52%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -3917,12 +3917,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>567810</t>
+          <t>566986</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>633029</t>
+          <t>627689</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3932,12 +3932,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>58,43%</t>
+          <t>58,35%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>65,14%</t>
+          <t>64,59%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3952,12 +3952,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>785205</t>
+          <t>785781</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>857845</t>
+          <t>857844</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3967,7 +3967,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>58,92%</t>
+          <t>58,97%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -3987,12 +3987,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1372549</t>
+          <t>1370410</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1466701</t>
+          <t>1469490</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4002,12 +4002,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>59,56%</t>
+          <t>59,47%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>63,65%</t>
+          <t>63,77%</t>
         </is>
       </c>
     </row>
@@ -4030,12 +4030,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>236927</t>
+          <t>236520</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>295643</t>
+          <t>295011</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4045,12 +4045,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>24,38%</t>
+          <t>24,34%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>30,42%</t>
+          <t>30,36%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4065,12 +4065,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>340567</t>
+          <t>339098</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>405457</t>
+          <t>405547</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4080,7 +4080,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>25,56%</t>
+          <t>25,45%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -4100,12 +4100,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>596440</t>
+          <t>597566</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>680886</t>
+          <t>685332</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4115,12 +4115,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>25,88%</t>
+          <t>25,93%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>29,55%</t>
+          <t>29,74%</t>
         </is>
       </c>
     </row>
@@ -4143,12 +4143,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>17537</t>
+          <t>16101</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>39403</t>
+          <t>37524</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4158,12 +4158,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4178,12 +4178,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>29959</t>
+          <t>30246</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>54489</t>
+          <t>56206</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4193,12 +4193,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4213,12 +4213,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>53748</t>
+          <t>52953</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>87444</t>
+          <t>88069</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4228,12 +4228,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,82%</t>
         </is>
       </c>
     </row>
@@ -4373,12 +4373,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>17798</t>
+          <t>18350</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>38853</t>
+          <t>39684</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4388,12 +4388,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4408,12 +4408,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>23863</t>
+          <t>24330</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>49237</t>
+          <t>49201</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -4443,12 +4443,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>47064</t>
+          <t>46060</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>81084</t>
+          <t>81431</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4458,12 +4458,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,19%</t>
         </is>
       </c>
     </row>
@@ -4486,12 +4486,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>131528</t>
+          <t>131667</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>177925</t>
+          <t>178953</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4506,7 +4506,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>9,07%</t>
+          <t>9,13%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4521,12 +4521,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>152151</t>
+          <t>151011</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>204089</t>
+          <t>201474</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4536,12 +4536,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>8,63%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>11,66%</t>
+          <t>11,51%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4556,12 +4556,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>294939</t>
+          <t>296906</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>367341</t>
+          <t>367109</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4571,12 +4571,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>8,0%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>9,9%</t>
+          <t>9,89%</t>
         </is>
       </c>
     </row>
@@ -4599,12 +4599,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1151598</t>
+          <t>1152648</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1241166</t>
+          <t>1242717</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4614,12 +4614,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>58,73%</t>
+          <t>58,78%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>63,3%</t>
+          <t>63,38%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4634,12 +4634,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1003906</t>
+          <t>1006160</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>1088307</t>
+          <t>1091922</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4649,12 +4649,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>57,36%</t>
+          <t>57,49%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>62,18%</t>
+          <t>62,39%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4669,12 +4669,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>2179613</t>
+          <t>2187104</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>2307094</t>
+          <t>2308334</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4684,12 +4684,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>58,73%</t>
+          <t>58,93%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>62,17%</t>
+          <t>62,2%</t>
         </is>
       </c>
     </row>
@@ -4712,12 +4712,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>503011</t>
+          <t>500684</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>583144</t>
+          <t>583137</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4727,7 +4727,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>25,65%</t>
+          <t>25,53%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -4747,12 +4747,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>405706</t>
+          <t>407143</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>480519</t>
+          <t>480838</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4762,12 +4762,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>23,18%</t>
+          <t>23,26%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>27,45%</t>
+          <t>27,47%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4782,12 +4782,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>927785</t>
+          <t>930757</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1037278</t>
+          <t>1040061</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4797,12 +4797,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>25,08%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>27,95%</t>
+          <t>28,03%</t>
         </is>
       </c>
     </row>
@@ -4825,12 +4825,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>29062</t>
+          <t>29756</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>55529</t>
+          <t>56791</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4840,12 +4840,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4860,12 +4860,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>35931</t>
+          <t>36269</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>65944</t>
+          <t>65956</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4875,7 +4875,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -4895,12 +4895,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>71074</t>
+          <t>72722</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>109223</t>
+          <t>109897</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4910,12 +4910,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,96%</t>
         </is>
       </c>
     </row>
@@ -5055,12 +5055,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2942</t>
+          <t>3734</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>14097</t>
+          <t>14450</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5070,12 +5070,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5090,12 +5090,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>8311</t>
+          <t>8258</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>22713</t>
+          <t>23925</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5105,12 +5105,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5125,12 +5125,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>14094</t>
+          <t>13649</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>32030</t>
+          <t>31697</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5140,12 +5140,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,38%</t>
         </is>
       </c>
     </row>
@@ -5168,12 +5168,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>46483</t>
+          <t>45691</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>77013</t>
+          <t>76239</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>9,54%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>16,07%</t>
+          <t>15,91%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5203,12 +5203,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>41019</t>
+          <t>40631</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>68972</t>
+          <t>69132</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5218,12 +5218,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>8,97%</t>
+          <t>8,88%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>15,08%</t>
+          <t>15,11%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5238,12 +5238,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>94615</t>
+          <t>94099</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>137896</t>
+          <t>136904</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5253,12 +5253,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>10,1%</t>
+          <t>10,05%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>14,72%</t>
+          <t>14,62%</t>
         </is>
       </c>
     </row>
@@ -5281,12 +5281,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>264313</t>
+          <t>265328</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>311759</t>
+          <t>311718</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5296,7 +5296,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>55,16%</t>
+          <t>55,37%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -5316,12 +5316,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>273757</t>
+          <t>274012</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>316846</t>
+          <t>318199</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5331,12 +5331,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>59,84%</t>
+          <t>59,9%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>69,26%</t>
+          <t>69,56%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5351,12 +5351,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>556045</t>
+          <t>552846</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>616698</t>
+          <t>618132</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5366,12 +5366,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>59,37%</t>
+          <t>59,03%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>65,84%</t>
+          <t>66,0%</t>
         </is>
       </c>
     </row>
@@ -5394,12 +5394,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>91950</t>
+          <t>91987</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>130324</t>
+          <t>132326</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5409,12 +5409,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>19,19%</t>
+          <t>19,2%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>27,2%</t>
+          <t>27,62%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5429,12 +5429,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>67130</t>
+          <t>65690</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>104428</t>
+          <t>101194</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5444,12 +5444,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>14,67%</t>
+          <t>14,36%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>22,83%</t>
+          <t>22,12%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5464,12 +5464,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>166955</t>
+          <t>168354</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>222355</t>
+          <t>220740</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5479,12 +5479,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>17,83%</t>
+          <t>17,97%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>23,74%</t>
+          <t>23,57%</t>
         </is>
       </c>
     </row>
@@ -5507,12 +5507,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>6327</t>
+          <t>6141</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>23557</t>
+          <t>23619</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5522,12 +5522,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5542,12 +5542,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>4980</t>
+          <t>4947</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>18342</t>
+          <t>18135</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5557,12 +5557,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>14007</t>
+          <t>13847</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>37510</t>
+          <t>35257</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5592,12 +5592,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>3,76%</t>
         </is>
       </c>
     </row>
@@ -5737,12 +5737,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>34179</t>
+          <t>35065</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>62963</t>
+          <t>62178</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5752,12 +5752,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5772,12 +5772,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>47699</t>
+          <t>46593</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>79897</t>
+          <t>81181</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5787,12 +5787,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5807,12 +5807,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>89445</t>
+          <t>89691</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>130614</t>
+          <t>132968</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5827,7 +5827,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,91%</t>
         </is>
       </c>
     </row>
@@ -5850,12 +5850,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>251737</t>
+          <t>247570</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>315134</t>
+          <t>313583</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5865,12 +5865,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>7,26%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>9,19%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>278899</t>
+          <t>281183</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>346544</t>
+          <t>349337</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5900,12 +5900,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>7,94%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>9,79%</t>
+          <t>9,87%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>552334</t>
+          <t>548631</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>646620</t>
+          <t>641270</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>7,89%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>9,3%</t>
+          <t>9,22%</t>
         </is>
       </c>
     </row>
@@ -5963,12 +5963,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>2026818</t>
+          <t>2019274</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>2141918</t>
+          <t>2136819</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -5978,12 +5978,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>59,41%</t>
+          <t>59,19%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>62,78%</t>
+          <t>62,63%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -5998,12 +5998,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>2102768</t>
+          <t>2105353</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>2220683</t>
+          <t>2220228</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>59,4%</t>
+          <t>59,47%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>62,73%</t>
+          <t>62,71%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>4168587</t>
+          <t>4160972</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>4334517</t>
+          <t>4334655</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6048,7 +6048,7 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>59,96%</t>
+          <t>59,85%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
@@ -6076,12 +6076,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>863782</t>
+          <t>868304</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>972243</t>
+          <t>977773</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6091,12 +6091,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>25,32%</t>
+          <t>25,45%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>28,5%</t>
+          <t>28,66%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6111,12 +6111,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>844988</t>
+          <t>849340</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>948430</t>
+          <t>952971</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6126,12 +6126,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>23,87%</t>
+          <t>23,99%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>26,79%</t>
+          <t>26,92%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1740658</t>
+          <t>1744150</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1892630</t>
+          <t>1892423</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6161,7 +6161,7 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>25,04%</t>
+          <t>25,09%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -6189,12 +6189,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>61057</t>
+          <t>62864</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>99280</t>
+          <t>97857</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6204,12 +6204,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6224,12 +6224,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>82137</t>
+          <t>81945</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>123515</t>
+          <t>124022</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6239,12 +6239,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6259,12 +6259,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>154307</t>
+          <t>152778</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>210507</t>
+          <t>208978</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6274,12 +6274,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,01%</t>
         </is>
       </c>
     </row>
@@ -6455,7 +6455,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la frecuencia de consumo de legumbres en 2016</t>
+          <t>Población según la frecuencia de consumo de legumbres en 2016 (tasa de respuesta: 99,6%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6650,12 +6650,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2891</t>
+          <t>3034</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>14209</t>
+          <t>15411</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6665,12 +6665,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6685,12 +6685,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4540</t>
+          <t>5058</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>18735</t>
+          <t>19625</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6700,12 +6700,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6720,12 +6720,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>10577</t>
+          <t>10979</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>28213</t>
+          <t>29047</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,67%</t>
         </is>
       </c>
     </row>
@@ -6763,12 +6763,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>31843</t>
+          <t>31516</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>56750</t>
+          <t>57699</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6778,12 +6778,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>7,67%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6798,12 +6798,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>46908</t>
+          <t>47900</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>80850</t>
+          <t>80834</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6813,7 +6813,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -6833,12 +6833,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>86759</t>
+          <t>84625</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>128594</t>
+          <t>124283</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6848,12 +6848,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>7,12%</t>
         </is>
       </c>
     </row>
@@ -6876,12 +6876,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>361109</t>
+          <t>362709</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>416594</t>
+          <t>414549</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6891,12 +6891,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>48,01%</t>
+          <t>48,22%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>55,38%</t>
+          <t>55,11%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6911,12 +6911,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>511513</t>
+          <t>511109</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>579192</t>
+          <t>576964</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6926,12 +6926,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>51,55%</t>
+          <t>51,51%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>58,37%</t>
+          <t>58,14%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6946,12 +6946,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>884270</t>
+          <t>889610</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>974031</t>
+          <t>972812</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6961,12 +6961,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>50,69%</t>
+          <t>50,99%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>55,83%</t>
+          <t>55,76%</t>
         </is>
       </c>
     </row>
@@ -6989,12 +6989,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>271904</t>
+          <t>270906</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>325214</t>
+          <t>321074</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7004,12 +7004,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>36,15%</t>
+          <t>36,01%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>43,23%</t>
+          <t>42,68%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7024,12 +7024,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>320600</t>
+          <t>322438</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>384732</t>
+          <t>383660</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7039,12 +7039,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>32,31%</t>
+          <t>32,49%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>38,77%</t>
+          <t>38,66%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>605354</t>
+          <t>605804</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>689318</t>
+          <t>687311</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7074,12 +7074,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>34,7%</t>
+          <t>34,73%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>39,51%</t>
+          <t>39,4%</t>
         </is>
       </c>
     </row>
@@ -7102,12 +7102,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>11302</t>
+          <t>10401</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>28892</t>
+          <t>28091</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7137,12 +7137,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>16117</t>
+          <t>15461</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>39031</t>
+          <t>37339</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7152,12 +7152,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7172,12 +7172,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>31604</t>
+          <t>31082</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>59524</t>
+          <t>59839</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7187,12 +7187,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,43%</t>
         </is>
       </c>
     </row>
@@ -7332,12 +7332,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>15955</t>
+          <t>16376</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>35203</t>
+          <t>35347</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7347,12 +7347,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7367,12 +7367,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>24676</t>
+          <t>24497</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>49311</t>
+          <t>49813</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7382,12 +7382,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7402,12 +7402,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>45948</t>
+          <t>45331</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>78404</t>
+          <t>77840</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7417,12 +7417,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,92%</t>
         </is>
       </c>
     </row>
@@ -7445,12 +7445,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>200919</t>
+          <t>199822</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>257061</t>
+          <t>259298</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>9,73%</t>
+          <t>9,68%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>12,45%</t>
+          <t>12,56%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>187949</t>
+          <t>187573</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>243206</t>
+          <t>242619</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7495,12 +7495,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>9,5%</t>
+          <t>9,48%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>12,29%</t>
+          <t>12,26%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7515,12 +7515,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>403334</t>
+          <t>401547</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>482799</t>
+          <t>482960</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7530,7 +7530,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>9,97%</t>
+          <t>9,93%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -7558,12 +7558,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1108234</t>
+          <t>1109721</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1197664</t>
+          <t>1200834</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>53,66%</t>
+          <t>53,74%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>57,99%</t>
+          <t>58,15%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7593,12 +7593,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1004413</t>
+          <t>1002469</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>1097533</t>
+          <t>1089745</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7608,12 +7608,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>50,76%</t>
+          <t>50,66%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>55,47%</t>
+          <t>55,08%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7628,12 +7628,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>2130738</t>
+          <t>2134834</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>2265682</t>
+          <t>2263506</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7643,12 +7643,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>52,69%</t>
+          <t>52,79%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>56,03%</t>
+          <t>55,98%</t>
         </is>
       </c>
     </row>
@@ -7671,12 +7671,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>567677</t>
+          <t>568305</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>655381</t>
+          <t>656851</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7686,12 +7686,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>27,49%</t>
+          <t>27,52%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>31,74%</t>
+          <t>31,81%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7706,12 +7706,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>587147</t>
+          <t>591222</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>672671</t>
+          <t>671540</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7721,12 +7721,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>29,67%</t>
+          <t>29,88%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>34,0%</t>
+          <t>33,94%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7741,12 +7741,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1183802</t>
+          <t>1181255</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1305001</t>
+          <t>1301597</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7756,12 +7756,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>29,27%</t>
+          <t>29,21%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>32,27%</t>
+          <t>32,19%</t>
         </is>
       </c>
     </row>
@@ -7784,12 +7784,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>33137</t>
+          <t>33989</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>63199</t>
+          <t>62573</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7799,82 +7799,82 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
+          <t>3,03%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>52192</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>39583</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>68779</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>2,64%</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>2,0%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>3,48%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>99611</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>81575</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>123676</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>2,46%</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>2,02%</t>
+        </is>
+      </c>
+      <c r="W14" s="2" t="inlineStr">
+        <is>
           <t>3,06%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>52192</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>38865</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>69609</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>2,64%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>1,96%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>3,52%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>91</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>99611</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>80993</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>122385</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>2,46%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>2,0%</t>
-        </is>
-      </c>
-      <c r="W14" s="2" t="inlineStr">
-        <is>
-          <t>3,03%</t>
         </is>
       </c>
     </row>
@@ -8019,7 +8019,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>6545</t>
+          <t>7545</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8034,7 +8034,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8049,12 +8049,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>4187</t>
+          <t>4124</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>17661</t>
+          <t>16921</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8064,12 +8064,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8084,12 +8084,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>5944</t>
+          <t>5879</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>20454</t>
+          <t>19523</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8104,7 +8104,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,79%</t>
         </is>
       </c>
     </row>
@@ -8127,12 +8127,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>52903</t>
+          <t>54339</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>86612</t>
+          <t>86027</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8142,12 +8142,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>9,72%</t>
+          <t>9,99%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>15,92%</t>
+          <t>15,81%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8162,12 +8162,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>57140</t>
+          <t>59185</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>90209</t>
+          <t>90522</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8177,12 +8177,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>10,41%</t>
+          <t>10,78%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>16,43%</t>
+          <t>16,48%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8197,12 +8197,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>123147</t>
+          <t>121715</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>167011</t>
+          <t>169356</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8212,12 +8212,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>11,26%</t>
+          <t>11,13%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>15,28%</t>
+          <t>15,49%</t>
         </is>
       </c>
     </row>
@@ -8240,12 +8240,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>293328</t>
+          <t>292202</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>342813</t>
+          <t>340609</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8255,12 +8255,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>53,91%</t>
+          <t>53,7%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>63,0%</t>
+          <t>62,6%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8275,12 +8275,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>315795</t>
+          <t>319395</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>362703</t>
+          <t>363863</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8290,12 +8290,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>57,51%</t>
+          <t>58,16%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>66,05%</t>
+          <t>66,26%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8310,12 +8310,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>622736</t>
+          <t>625764</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>691368</t>
+          <t>693599</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8325,12 +8325,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>56,96%</t>
+          <t>57,24%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>63,24%</t>
+          <t>63,44%</t>
         </is>
       </c>
     </row>
@@ -8353,12 +8353,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>125828</t>
+          <t>126071</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>169620</t>
+          <t>170794</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>23,12%</t>
+          <t>23,17%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>31,17%</t>
+          <t>31,39%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8388,12 +8388,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>100685</t>
+          <t>100114</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>141558</t>
+          <t>139089</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8403,12 +8403,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>18,34%</t>
+          <t>18,23%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>25,78%</t>
+          <t>25,33%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>239107</t>
+          <t>235422</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>298456</t>
+          <t>293848</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8438,12 +8438,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>21,87%</t>
+          <t>21,53%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>27,3%</t>
+          <t>26,88%</t>
         </is>
       </c>
     </row>
@@ -8466,12 +8466,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>4112</t>
+          <t>4183</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>16333</t>
+          <t>16819</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8481,12 +8481,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8501,12 +8501,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>2288</t>
+          <t>2100</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>13789</t>
+          <t>13051</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8516,12 +8516,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>8011</t>
+          <t>8937</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>25051</t>
+          <t>26205</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8551,12 +8551,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,4%</t>
         </is>
       </c>
     </row>
@@ -8696,12 +8696,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>23673</t>
+          <t>24345</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>48833</t>
+          <t>48314</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8711,12 +8711,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8731,12 +8731,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>41753</t>
+          <t>42501</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>71956</t>
+          <t>72411</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8746,12 +8746,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>72965</t>
+          <t>71114</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>111379</t>
+          <t>110464</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8781,12 +8781,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,61%</t>
         </is>
       </c>
     </row>
@@ -8809,12 +8809,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>307160</t>
+          <t>307503</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>380068</t>
+          <t>378182</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8824,12 +8824,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>9,14%</t>
+          <t>9,15%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>11,31%</t>
+          <t>11,25%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>312200</t>
+          <t>313367</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>387332</t>
+          <t>387354</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8859,7 +8859,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>8,87%</t>
+          <t>8,9%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>634308</t>
+          <t>635827</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>742306</t>
+          <t>733670</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8894,12 +8894,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
+          <t>9,24%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>10,79%</t>
+          <t>10,66%</t>
         </is>
       </c>
     </row>
@@ -8922,12 +8922,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1796075</t>
+          <t>1794046</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>1915639</t>
+          <t>1916502</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8937,12 +8937,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>53,43%</t>
+          <t>53,37%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>56,99%</t>
+          <t>57,01%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8957,12 +8957,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1874262</t>
+          <t>1868679</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>1989706</t>
+          <t>1988177</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8972,12 +8972,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>53,25%</t>
+          <t>53,09%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>56,52%</t>
+          <t>56,48%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8992,12 +8992,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>3704882</t>
+          <t>3702302</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>3869805</t>
+          <t>3877282</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9007,12 +9007,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>53,84%</t>
+          <t>53,8%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>56,23%</t>
+          <t>56,34%</t>
         </is>
       </c>
     </row>
@@ -9035,12 +9035,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>998602</t>
+          <t>1003980</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1114297</t>
+          <t>1112546</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9050,12 +9050,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>29,71%</t>
+          <t>29,87%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>33,15%</t>
+          <t>33,1%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9070,12 +9070,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1046815</t>
+          <t>1045026</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1160128</t>
+          <t>1159945</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9085,12 +9085,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>29,74%</t>
+          <t>29,69%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>32,96%</t>
+          <t>32,95%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9105,12 +9105,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>2074043</t>
+          <t>2074303</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>2230799</t>
+          <t>2234099</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9125,7 +9125,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>32,42%</t>
+          <t>32,47%</t>
         </is>
       </c>
     </row>
@@ -9148,12 +9148,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>58493</t>
+          <t>56650</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>91661</t>
+          <t>92760</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9163,12 +9163,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9183,12 +9183,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>66246</t>
+          <t>65542</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>104840</t>
+          <t>104974</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9198,7 +9198,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -9218,12 +9218,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>133049</t>
+          <t>132885</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>185112</t>
+          <t>186331</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9238,7 +9238,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,71%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P36B04-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P36B04-Estudios-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5700</t>
+          <t>6164</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>21274</t>
+          <t>21102</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>9712</t>
+          <t>9576</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>27147</t>
+          <t>27299</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>18156</t>
+          <t>19033</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>42617</t>
+          <t>41174</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,76%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>71162</t>
+          <t>70398</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>106000</t>
+          <t>105884</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>6,83%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>10,28%</t>
+          <t>10,27%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>84123</t>
+          <t>82028</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>122467</t>
+          <t>124062</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>9,43%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>162878</t>
+          <t>159893</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>217616</t>
+          <t>214865</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>6,82%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>9,28%</t>
+          <t>9,16%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>555187</t>
+          <t>552761</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>615187</t>
+          <t>613536</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>53,86%</t>
+          <t>53,62%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>59,68%</t>
+          <t>59,52%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>754887</t>
+          <t>757846</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>828853</t>
+          <t>830213</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>57,4%</t>
+          <t>57,63%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>63,03%</t>
+          <t>63,13%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1328846</t>
+          <t>1331705</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1424190</t>
+          <t>1428892</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>56,64%</t>
+          <t>56,77%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>60,71%</t>
+          <t>60,91%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>297647</t>
+          <t>300533</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>355456</t>
+          <t>358730</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>28,87%</t>
+          <t>29,15%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>34,48%</t>
+          <t>34,8%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>347980</t>
+          <t>349325</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>414016</t>
+          <t>415719</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>26,46%</t>
+          <t>26,56%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>31,48%</t>
+          <t>31,61%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>666805</t>
+          <t>662067</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>751638</t>
+          <t>751967</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>28,42%</t>
+          <t>28,22%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>32,04%</t>
+          <t>32,05%</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>10906</t>
+          <t>11132</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>27643</t>
+          <t>27695</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1219,12 +1219,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>13953</t>
+          <t>13346</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>32651</t>
+          <t>32976</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1234,12 +1234,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>29386</t>
+          <t>29729</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>53483</t>
+          <t>54818</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1269,12 +1269,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,34%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>11430</t>
+          <t>10772</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>28747</t>
+          <t>28745</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,7 +1429,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>14181</t>
+          <t>14663</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>33402</t>
+          <t>32966</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>29998</t>
+          <t>28521</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>54156</t>
+          <t>56124</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,71%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>209235</t>
+          <t>211383</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>265645</t>
+          <t>266523</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>12,36%</t>
+          <t>12,48%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>15,69%</t>
+          <t>15,74%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>133006</t>
+          <t>135385</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>178498</t>
+          <t>182005</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>8,54%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>11,27%</t>
+          <t>11,49%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>356605</t>
+          <t>358867</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>429221</t>
+          <t>437271</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>10,88%</t>
+          <t>10,95%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>13,09%</t>
+          <t>13,34%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>970751</t>
+          <t>972879</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1046249</t>
+          <t>1049185</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>57,33%</t>
+          <t>57,45%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>61,78%</t>
+          <t>61,96%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>963788</t>
+          <t>962692</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>1038330</t>
+          <t>1038329</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,7 +1690,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>60,83%</t>
+          <t>60,76%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1960725</t>
+          <t>1950737</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>2072641</t>
+          <t>2065077</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>59,82%</t>
+          <t>59,51%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>63,23%</t>
+          <t>63,0%</t>
         </is>
       </c>
     </row>
@@ -1753,12 +1753,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>370640</t>
+          <t>368449</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>439531</t>
+          <t>440905</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1768,12 +1768,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>21,89%</t>
+          <t>21,76%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>25,96%</t>
+          <t>26,04%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1788,12 +1788,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>352971</t>
+          <t>352606</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>422258</t>
+          <t>419633</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1803,12 +1803,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>22,28%</t>
+          <t>22,25%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>26,65%</t>
+          <t>26,48%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>742963</t>
+          <t>742249</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>836587</t>
+          <t>840358</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>22,67%</t>
+          <t>22,64%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>25,52%</t>
+          <t>25,64%</t>
         </is>
       </c>
     </row>
@@ -1866,12 +1866,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>15188</t>
+          <t>14923</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>34882</t>
+          <t>34231</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1901,12 +1901,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>11874</t>
+          <t>12229</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>31074</t>
+          <t>29870</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1916,12 +1916,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>31398</t>
+          <t>31716</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>57351</t>
+          <t>58567</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1951,12 +1951,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,79%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3269</t>
+          <t>3277</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>14622</t>
+          <t>15510</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2116,7 +2116,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>4113</t>
+          <t>4187</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>16893</t>
+          <t>16849</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>9244</t>
+          <t>9388</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>25633</t>
+          <t>26704</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,6%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>75808</t>
+          <t>76915</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>111374</t>
+          <t>111015</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>13,75%</t>
+          <t>13,95%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>20,2%</t>
+          <t>20,13%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>32846</t>
+          <t>32005</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>59841</t>
+          <t>57638</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>6,72%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>12,56%</t>
+          <t>12,1%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>114663</t>
+          <t>115807</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>162013</t>
+          <t>161478</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>11,16%</t>
+          <t>11,27%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>15,76%</t>
+          <t>15,71%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>320496</t>
+          <t>320206</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>367509</t>
+          <t>365165</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>58,12%</t>
+          <t>58,07%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>66,65%</t>
+          <t>66,22%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>296268</t>
+          <t>298064</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>339948</t>
+          <t>340741</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>62,19%</t>
+          <t>62,56%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>71,36%</t>
+          <t>71,52%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>633089</t>
+          <t>629735</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>695813</t>
+          <t>694303</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>61,6%</t>
+          <t>61,27%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>67,7%</t>
+          <t>67,55%</t>
         </is>
       </c>
     </row>
@@ -2435,12 +2435,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>83822</t>
+          <t>83347</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>121453</t>
+          <t>121044</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2450,12 +2450,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>15,2%</t>
+          <t>15,12%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>22,03%</t>
+          <t>21,95%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2470,12 +2470,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>80425</t>
+          <t>79748</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>116872</t>
+          <t>117473</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2485,12 +2485,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>16,88%</t>
+          <t>16,74%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>24,53%</t>
+          <t>24,66%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>176195</t>
+          <t>178470</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>228149</t>
+          <t>230970</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>17,14%</t>
+          <t>17,36%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>22,2%</t>
+          <t>22,47%</t>
         </is>
       </c>
     </row>
@@ -2548,12 +2548,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2299</t>
+          <t>1752</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>14703</t>
+          <t>13546</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2583,12 +2583,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>2129</t>
+          <t>2123</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>12205</t>
+          <t>12247</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2603,7 +2603,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>6419</t>
+          <t>6685</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>21425</t>
+          <t>22375</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2633,12 +2633,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,18%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>25992</t>
+          <t>28077</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>51886</t>
+          <t>53174</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>34629</t>
+          <t>34353</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>63120</t>
+          <t>62129</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,47 +2828,47 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
+          <t>1,02%</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>1,84%</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t>85707</t>
+        </is>
+      </c>
+      <c r="S22" s="2" t="inlineStr">
+        <is>
+          <t>68418</t>
+        </is>
+      </c>
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t>106181</t>
+        </is>
+      </c>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>1,29%</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
           <t>1,03%</t>
         </is>
       </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>1,87%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>81</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>85707</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>69288</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>105400</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>1,29%</t>
-        </is>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>1,04%</t>
-        </is>
-      </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,6%</t>
         </is>
       </c>
     </row>
@@ -2891,12 +2891,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>376843</t>
+          <t>379548</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>453484</t>
+          <t>456868</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2906,12 +2906,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>11,5%</t>
+          <t>11,59%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>13,84%</t>
+          <t>13,95%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>266845</t>
+          <t>270576</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>332759</t>
+          <t>339202</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2941,12 +2941,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>8,01%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>9,86%</t>
+          <t>10,05%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>664443</t>
+          <t>670329</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>772591</t>
+          <t>770317</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>9,99%</t>
+          <t>10,08%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>11,62%</t>
+          <t>11,58%</t>
         </is>
       </c>
     </row>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1880651</t>
+          <t>1879227</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>1999380</t>
+          <t>1996366</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3019,12 +3019,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>57,41%</t>
+          <t>57,37%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>61,04%</t>
+          <t>60,95%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>2060570</t>
+          <t>2055617</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>2170249</t>
+          <t>2168400</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3054,12 +3054,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>61,04%</t>
+          <t>60,89%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>64,29%</t>
+          <t>64,23%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>3977594</t>
+          <t>3970636</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>4137982</t>
+          <t>4130882</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>59,8%</t>
+          <t>59,69%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>62,21%</t>
+          <t>62,1%</t>
         </is>
       </c>
     </row>
@@ -3117,12 +3117,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>790027</t>
+          <t>784171</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>890315</t>
+          <t>885117</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>24,12%</t>
+          <t>23,94%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>27,18%</t>
+          <t>27,02%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3152,12 +3152,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>813721</t>
+          <t>815608</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>915619</t>
+          <t>916465</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>24,1%</t>
+          <t>24,16%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>27,12%</t>
+          <t>27,15%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1627085</t>
+          <t>1622078</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1771672</t>
+          <t>1772027</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3202,7 +3202,7 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>24,46%</t>
+          <t>24,39%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -3230,12 +3230,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>35391</t>
+          <t>35576</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>61438</t>
+          <t>63364</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3245,12 +3245,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3265,12 +3265,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>34894</t>
+          <t>35822</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>62499</t>
+          <t>62264</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3300,12 +3300,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>77619</t>
+          <t>76847</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>115112</t>
+          <t>115085</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3315,7 +3315,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -3691,12 +3691,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6511</t>
+          <t>6475</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>20854</t>
+          <t>21865</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3711,7 +3711,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>6552</t>
+          <t>6665</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>22778</t>
+          <t>22616</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3741,12 +3741,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>15917</t>
+          <t>16578</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>37534</t>
+          <t>39069</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3776,12 +3776,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,7%</t>
         </is>
       </c>
     </row>
@@ -3804,12 +3804,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>53664</t>
+          <t>53777</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>86736</t>
+          <t>86521</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3819,12 +3819,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>8,93%</t>
+          <t>8,9%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>64850</t>
+          <t>65838</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>100107</t>
+          <t>104147</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3854,12 +3854,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>127308</t>
+          <t>127005</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>176660</t>
+          <t>175245</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3889,12 +3889,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>5,51%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>7,6%</t>
         </is>
       </c>
     </row>
@@ -3917,12 +3917,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>566986</t>
+          <t>569399</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>627689</t>
+          <t>628972</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3932,12 +3932,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>58,35%</t>
+          <t>58,59%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>64,59%</t>
+          <t>64,72%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3952,12 +3952,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>785781</t>
+          <t>787252</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>857844</t>
+          <t>859963</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3967,12 +3967,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>58,97%</t>
+          <t>59,08%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>64,37%</t>
+          <t>64,53%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3987,12 +3987,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1370410</t>
+          <t>1378047</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1469490</t>
+          <t>1467990</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4002,12 +4002,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>59,47%</t>
+          <t>59,8%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>63,77%</t>
+          <t>63,7%</t>
         </is>
       </c>
     </row>
@@ -4030,12 +4030,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>236520</t>
+          <t>237857</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>295011</t>
+          <t>293323</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4045,12 +4045,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>24,34%</t>
+          <t>24,48%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>30,36%</t>
+          <t>30,18%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4065,12 +4065,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>339098</t>
+          <t>337991</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>405547</t>
+          <t>406274</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4080,12 +4080,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>25,45%</t>
+          <t>25,36%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>30,43%</t>
+          <t>30,49%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4100,12 +4100,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>597566</t>
+          <t>592433</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>685332</t>
+          <t>679023</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4115,12 +4115,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>25,93%</t>
+          <t>25,71%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>29,74%</t>
+          <t>29,47%</t>
         </is>
       </c>
     </row>
@@ -4143,12 +4143,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>16101</t>
+          <t>17022</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>37524</t>
+          <t>38155</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4158,12 +4158,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4178,12 +4178,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>30246</t>
+          <t>30232</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>56206</t>
+          <t>56082</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4198,7 +4198,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4213,12 +4213,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>52953</t>
+          <t>53599</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>88069</t>
+          <t>87092</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4228,12 +4228,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,78%</t>
         </is>
       </c>
     </row>
@@ -4373,12 +4373,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>18350</t>
+          <t>18452</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>39684</t>
+          <t>39351</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4393,7 +4393,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4408,12 +4408,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>24330</t>
+          <t>22520</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>49201</t>
+          <t>50466</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4423,12 +4423,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4443,12 +4443,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>46060</t>
+          <t>47505</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>81431</t>
+          <t>81122</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4458,7 +4458,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -4486,12 +4486,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>131667</t>
+          <t>132186</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>178953</t>
+          <t>178018</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4501,12 +4501,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>6,74%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>9,08%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4521,12 +4521,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>151011</t>
+          <t>150194</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>201474</t>
+          <t>203088</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4536,12 +4536,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>8,58%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>11,51%</t>
+          <t>11,6%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4556,12 +4556,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>296906</t>
+          <t>294798</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>367109</t>
+          <t>365754</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4571,12 +4571,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>7,94%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>9,89%</t>
+          <t>9,86%</t>
         </is>
       </c>
     </row>
@@ -4599,12 +4599,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1152648</t>
+          <t>1147837</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1242717</t>
+          <t>1237789</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4614,12 +4614,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>58,78%</t>
+          <t>58,54%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>63,38%</t>
+          <t>63,12%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4634,12 +4634,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1006160</t>
+          <t>1008031</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>1091922</t>
+          <t>1086225</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4649,12 +4649,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>57,49%</t>
+          <t>57,59%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>62,39%</t>
+          <t>62,06%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4669,12 +4669,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>2187104</t>
+          <t>2183670</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>2308334</t>
+          <t>2305369</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4684,12 +4684,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>58,93%</t>
+          <t>58,84%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>62,2%</t>
+          <t>62,12%</t>
         </is>
       </c>
     </row>
@@ -4712,12 +4712,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>500684</t>
+          <t>503047</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>583137</t>
+          <t>587880</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4727,12 +4727,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>25,53%</t>
+          <t>25,65%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>29,74%</t>
+          <t>29,98%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4747,12 +4747,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>407143</t>
+          <t>406918</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>480838</t>
+          <t>480712</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4762,7 +4762,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>23,26%</t>
+          <t>23,25%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -4782,12 +4782,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>930757</t>
+          <t>927487</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1040061</t>
+          <t>1040458</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4797,12 +4797,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>25,08%</t>
+          <t>24,99%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>28,03%</t>
+          <t>28,04%</t>
         </is>
       </c>
     </row>
@@ -4825,12 +4825,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>29756</t>
+          <t>28598</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>56791</t>
+          <t>55055</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4840,12 +4840,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4860,12 +4860,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>36269</t>
+          <t>35575</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>65956</t>
+          <t>64859</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4875,12 +4875,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4895,12 +4895,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>72722</t>
+          <t>71003</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>109897</t>
+          <t>109870</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4910,7 +4910,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3734</t>
+          <t>2955</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>14450</t>
+          <t>14232</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5070,12 +5070,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5090,12 +5090,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>8258</t>
+          <t>8129</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>23925</t>
+          <t>22723</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5105,12 +5105,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>4,97%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5125,12 +5125,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>13649</t>
+          <t>14513</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>31697</t>
+          <t>31364</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5140,12 +5140,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,35%</t>
         </is>
       </c>
     </row>
@@ -5168,12 +5168,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>45691</t>
+          <t>45434</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>76239</t>
+          <t>77264</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>9,54%</t>
+          <t>9,48%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>15,91%</t>
+          <t>16,13%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5203,12 +5203,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>40631</t>
+          <t>41188</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>69132</t>
+          <t>71481</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5218,12 +5218,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>8,88%</t>
+          <t>9,0%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>15,11%</t>
+          <t>15,63%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5238,12 +5238,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>94099</t>
+          <t>93930</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>136904</t>
+          <t>135583</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5253,12 +5253,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>10,05%</t>
+          <t>10,03%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>14,62%</t>
+          <t>14,48%</t>
         </is>
       </c>
     </row>
@@ -5281,12 +5281,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>265328</t>
+          <t>266378</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>311718</t>
+          <t>313289</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5296,12 +5296,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>55,37%</t>
+          <t>55,59%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>65,06%</t>
+          <t>65,38%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5316,12 +5316,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>274012</t>
+          <t>271705</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>318199</t>
+          <t>316270</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5331,12 +5331,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>59,9%</t>
+          <t>59,39%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>69,56%</t>
+          <t>69,13%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5351,12 +5351,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>552846</t>
+          <t>550623</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>618132</t>
+          <t>616776</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5366,12 +5366,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>59,03%</t>
+          <t>58,79%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>66,0%</t>
+          <t>65,85%</t>
         </is>
       </c>
     </row>
@@ -5394,12 +5394,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>91987</t>
+          <t>92168</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>132326</t>
+          <t>131023</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5409,12 +5409,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>19,2%</t>
+          <t>19,24%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>27,62%</t>
+          <t>27,34%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5429,12 +5429,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>65690</t>
+          <t>69328</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>101194</t>
+          <t>105367</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5444,12 +5444,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>14,36%</t>
+          <t>15,15%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>22,12%</t>
+          <t>23,03%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5464,12 +5464,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>168354</t>
+          <t>169179</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>220740</t>
+          <t>222617</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5479,12 +5479,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>17,97%</t>
+          <t>18,06%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>23,57%</t>
+          <t>23,77%</t>
         </is>
       </c>
     </row>
@@ -5507,12 +5507,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>6141</t>
+          <t>6129</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>23619</t>
+          <t>23062</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5527,7 +5527,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5542,12 +5542,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>4947</t>
+          <t>4982</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>18135</t>
+          <t>17895</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5557,12 +5557,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>13847</t>
+          <t>13719</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>35257</t>
+          <t>34882</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5592,12 +5592,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,72%</t>
         </is>
       </c>
     </row>
@@ -5737,12 +5737,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>35065</t>
+          <t>35133</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>62178</t>
+          <t>63989</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5757,7 +5757,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5772,12 +5772,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>46593</t>
+          <t>47924</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>81181</t>
+          <t>79587</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5787,12 +5787,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5807,12 +5807,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>89691</t>
+          <t>89890</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>132968</t>
+          <t>133899</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5827,7 +5827,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,93%</t>
         </is>
       </c>
     </row>
@@ -5850,12 +5850,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>247570</t>
+          <t>248818</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>313583</t>
+          <t>317170</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5865,12 +5865,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>7,29%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>9,19%</t>
+          <t>9,3%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>281183</t>
+          <t>279940</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>349337</t>
+          <t>350763</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5900,12 +5900,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>7,91%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>9,87%</t>
+          <t>9,91%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>548631</t>
+          <t>547152</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>641270</t>
+          <t>644458</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>7,87%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
+          <t>9,27%</t>
         </is>
       </c>
     </row>
@@ -5963,12 +5963,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>2019274</t>
+          <t>2026795</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>2136819</t>
+          <t>2145263</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -5978,12 +5978,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>59,19%</t>
+          <t>59,41%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>62,63%</t>
+          <t>62,88%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -5998,12 +5998,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>2105353</t>
+          <t>2106301</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>2220228</t>
+          <t>2223409</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>59,47%</t>
+          <t>59,49%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>62,71%</t>
+          <t>62,8%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>4160972</t>
+          <t>4171389</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>4334655</t>
+          <t>4332577</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>59,85%</t>
+          <t>60,0%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>62,35%</t>
+          <t>62,32%</t>
         </is>
       </c>
     </row>
@@ -6076,12 +6076,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>868304</t>
+          <t>868871</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>977773</t>
+          <t>975502</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6091,12 +6091,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>25,45%</t>
+          <t>25,47%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>28,66%</t>
+          <t>28,59%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6111,12 +6111,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>849340</t>
+          <t>848371</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>952971</t>
+          <t>957170</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6126,12 +6126,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>23,99%</t>
+          <t>23,96%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>26,92%</t>
+          <t>27,04%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1744150</t>
+          <t>1744430</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1892423</t>
+          <t>1895747</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6166,7 +6166,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>27,22%</t>
+          <t>27,27%</t>
         </is>
       </c>
     </row>
@@ -6189,12 +6189,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>62864</t>
+          <t>62075</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>97857</t>
+          <t>99890</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6204,12 +6204,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6229,7 +6229,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>124022</t>
+          <t>124837</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6244,7 +6244,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6259,12 +6259,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>152778</t>
+          <t>154564</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>208978</t>
+          <t>210905</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6274,12 +6274,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>3,03%</t>
         </is>
       </c>
     </row>
@@ -6650,12 +6650,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3034</t>
+          <t>2901</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>15411</t>
+          <t>14505</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6665,12 +6665,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6685,12 +6685,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>5058</t>
+          <t>4611</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>19625</t>
+          <t>18805</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6700,12 +6700,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6720,12 +6720,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>10979</t>
+          <t>10924</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>29047</t>
+          <t>29802</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6740,7 +6740,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,71%</t>
         </is>
       </c>
     </row>
@@ -6763,12 +6763,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>31516</t>
+          <t>32050</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>57699</t>
+          <t>57545</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6778,12 +6778,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>7,65%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6798,12 +6798,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>47900</t>
+          <t>46551</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>80834</t>
+          <t>77777</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6813,12 +6813,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>7,84%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6833,12 +6833,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>84625</t>
+          <t>84468</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>124283</t>
+          <t>127547</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6848,12 +6848,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>7,31%</t>
         </is>
       </c>
     </row>
@@ -6876,12 +6876,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>362709</t>
+          <t>362139</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>414549</t>
+          <t>415520</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6891,12 +6891,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>48,22%</t>
+          <t>48,14%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>55,11%</t>
+          <t>55,24%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6911,12 +6911,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>511109</t>
+          <t>510111</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>576964</t>
+          <t>573333</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6926,12 +6926,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>51,51%</t>
+          <t>51,41%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>58,14%</t>
+          <t>57,78%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6946,12 +6946,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>889610</t>
+          <t>889501</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>972812</t>
+          <t>975605</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6966,7 +6966,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>55,76%</t>
+          <t>55,92%</t>
         </is>
       </c>
     </row>
@@ -6989,12 +6989,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>270906</t>
+          <t>270837</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>321074</t>
+          <t>323126</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7009,7 +7009,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>42,68%</t>
+          <t>42,96%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7024,12 +7024,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>322438</t>
+          <t>320510</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>383660</t>
+          <t>383268</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7039,12 +7039,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>32,49%</t>
+          <t>32,3%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>38,66%</t>
+          <t>38,62%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>605804</t>
+          <t>606671</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>687311</t>
+          <t>689162</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7074,12 +7074,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>34,73%</t>
+          <t>34,78%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>39,4%</t>
+          <t>39,5%</t>
         </is>
       </c>
     </row>
@@ -7102,12 +7102,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>10401</t>
+          <t>11371</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>28091</t>
+          <t>28558</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7137,12 +7137,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>15461</t>
+          <t>16019</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>37339</t>
+          <t>37336</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7152,7 +7152,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -7172,12 +7172,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>31082</t>
+          <t>30607</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>59839</t>
+          <t>57383</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7187,12 +7187,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,29%</t>
         </is>
       </c>
     </row>
@@ -7332,12 +7332,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>16376</t>
+          <t>15392</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>35347</t>
+          <t>34319</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7347,12 +7347,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7367,12 +7367,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>24497</t>
+          <t>26439</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>49813</t>
+          <t>52468</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7382,12 +7382,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7402,12 +7402,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>45331</t>
+          <t>47019</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>77840</t>
+          <t>78676</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7417,12 +7417,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,95%</t>
         </is>
       </c>
     </row>
@@ -7445,12 +7445,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>199822</t>
+          <t>197023</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>259298</t>
+          <t>256361</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>9,68%</t>
+          <t>9,54%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>12,56%</t>
+          <t>12,41%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>187573</t>
+          <t>186821</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>242619</t>
+          <t>245549</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7495,12 +7495,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>9,48%</t>
+          <t>9,44%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>12,41%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7515,12 +7515,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>401547</t>
+          <t>400769</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>482960</t>
+          <t>484161</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>9,93%</t>
+          <t>9,91%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>11,94%</t>
+          <t>11,97%</t>
         </is>
       </c>
     </row>
@@ -7558,12 +7558,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1109721</t>
+          <t>1108326</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1200834</t>
+          <t>1199520</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>53,74%</t>
+          <t>53,67%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>58,15%</t>
+          <t>58,08%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7593,12 +7593,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1002469</t>
+          <t>1001216</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>1089745</t>
+          <t>1091093</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7608,12 +7608,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>50,66%</t>
+          <t>50,6%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>55,08%</t>
+          <t>55,14%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7628,12 +7628,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>2134834</t>
+          <t>2134281</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>2263506</t>
+          <t>2256823</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7643,12 +7643,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>52,79%</t>
+          <t>52,78%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>55,98%</t>
+          <t>55,81%</t>
         </is>
       </c>
     </row>
@@ -7671,12 +7671,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>568305</t>
+          <t>574679</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>656851</t>
+          <t>657425</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7686,47 +7686,47 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>27,52%</t>
+          <t>27,83%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
+          <t>31,83%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>600</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>629346</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>584915</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>673600</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
           <t>31,81%</t>
         </is>
       </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>600</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>629346</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>591222</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>671540</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>31,81%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>29,88%</t>
+          <t>29,56%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>33,94%</t>
+          <t>34,04%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7741,12 +7741,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1181255</t>
+          <t>1183492</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1301597</t>
+          <t>1305204</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7756,12 +7756,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>29,21%</t>
+          <t>29,27%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>32,19%</t>
+          <t>32,28%</t>
         </is>
       </c>
     </row>
@@ -7784,12 +7784,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>33989</t>
+          <t>33451</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>62573</t>
+          <t>63954</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7799,12 +7799,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7819,12 +7819,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>39583</t>
+          <t>39488</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>68779</t>
+          <t>68072</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7839,7 +7839,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7854,12 +7854,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>81575</t>
+          <t>81914</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>123676</t>
+          <t>121900</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7869,12 +7869,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,01%</t>
         </is>
       </c>
     </row>
@@ -8019,7 +8019,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>7545</t>
+          <t>7519</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8034,7 +8034,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8049,12 +8049,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>4124</t>
+          <t>4874</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>16921</t>
+          <t>17916</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8064,12 +8064,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8089,7 +8089,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>19523</t>
+          <t>18898</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8104,7 +8104,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,73%</t>
         </is>
       </c>
     </row>
@@ -8127,12 +8127,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>54339</t>
+          <t>52513</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>86027</t>
+          <t>88100</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8142,12 +8142,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>9,99%</t>
+          <t>9,65%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>15,81%</t>
+          <t>16,19%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8162,12 +8162,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>59185</t>
+          <t>59528</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>90522</t>
+          <t>91236</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8177,12 +8177,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>10,78%</t>
+          <t>10,84%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>16,48%</t>
+          <t>16,61%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8197,12 +8197,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>121715</t>
+          <t>120153</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>169356</t>
+          <t>167270</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8212,12 +8212,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>11,13%</t>
+          <t>10,99%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>15,49%</t>
+          <t>15,3%</t>
         </is>
       </c>
     </row>
@@ -8240,12 +8240,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>292202</t>
+          <t>291657</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>340609</t>
+          <t>339846</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8255,12 +8255,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>53,7%</t>
+          <t>53,6%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>62,6%</t>
+          <t>62,46%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8275,12 +8275,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>319395</t>
+          <t>316422</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>363863</t>
+          <t>362629</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8290,12 +8290,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>58,16%</t>
+          <t>57,62%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>66,26%</t>
+          <t>66,04%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8310,12 +8310,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>625764</t>
+          <t>626005</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>693599</t>
+          <t>691888</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8325,12 +8325,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>57,24%</t>
+          <t>57,26%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>63,44%</t>
+          <t>63,29%</t>
         </is>
       </c>
     </row>
@@ -8353,12 +8353,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>126071</t>
+          <t>125427</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>170794</t>
+          <t>168977</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>23,17%</t>
+          <t>23,05%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>31,39%</t>
+          <t>31,05%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8388,12 +8388,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>100114</t>
+          <t>101771</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>139089</t>
+          <t>141213</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8403,12 +8403,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>18,23%</t>
+          <t>18,53%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>25,33%</t>
+          <t>25,72%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>235422</t>
+          <t>238169</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>293848</t>
+          <t>295042</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8438,12 +8438,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>21,53%</t>
+          <t>21,78%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>26,88%</t>
+          <t>26,99%</t>
         </is>
       </c>
     </row>
@@ -8466,12 +8466,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>4183</t>
+          <t>4259</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>16819</t>
+          <t>17150</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8481,12 +8481,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8501,12 +8501,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>2100</t>
+          <t>3038</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>13051</t>
+          <t>14567</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8516,12 +8516,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>8937</t>
+          <t>8558</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>26205</t>
+          <t>24977</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8551,12 +8551,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,28%</t>
         </is>
       </c>
     </row>
@@ -8696,12 +8696,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>24345</t>
+          <t>23650</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>48314</t>
+          <t>46176</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8711,12 +8711,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8731,12 +8731,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>42501</t>
+          <t>41856</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>72411</t>
+          <t>71384</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8746,12 +8746,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>71114</t>
+          <t>71550</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>110464</t>
+          <t>110260</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8781,12 +8781,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,6%</t>
         </is>
       </c>
     </row>
@@ -8809,12 +8809,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>307503</t>
+          <t>304614</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>378182</t>
+          <t>376425</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8824,12 +8824,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>9,15%</t>
+          <t>9,06%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>11,25%</t>
+          <t>11,2%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>313367</t>
+          <t>313323</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>387354</t>
+          <t>385225</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8864,7 +8864,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>11,0%</t>
+          <t>10,94%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>635827</t>
+          <t>635752</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>733670</t>
+          <t>738286</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8899,7 +8899,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>10,66%</t>
+          <t>10,73%</t>
         </is>
       </c>
     </row>
@@ -8922,12 +8922,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1794046</t>
+          <t>1796459</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>1916502</t>
+          <t>1914428</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8937,12 +8937,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>53,37%</t>
+          <t>53,44%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>57,01%</t>
+          <t>56,95%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8957,12 +8957,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1868679</t>
+          <t>1870000</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>1988177</t>
+          <t>1987578</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8972,12 +8972,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>53,09%</t>
+          <t>53,12%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>56,48%</t>
+          <t>56,46%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8992,12 +8992,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>3702302</t>
+          <t>3706509</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>3877282</t>
+          <t>3871003</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9007,12 +9007,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>53,8%</t>
+          <t>53,86%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>56,34%</t>
+          <t>56,25%</t>
         </is>
       </c>
     </row>
@@ -9035,12 +9035,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1003980</t>
+          <t>1000369</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1112546</t>
+          <t>1113875</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9050,12 +9050,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>29,87%</t>
+          <t>29,76%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>33,1%</t>
+          <t>33,14%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9070,12 +9070,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1045026</t>
+          <t>1047994</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1159945</t>
+          <t>1164611</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9085,12 +9085,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>29,69%</t>
+          <t>29,77%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>32,95%</t>
+          <t>33,08%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9105,12 +9105,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>2074303</t>
+          <t>2072973</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>2234099</t>
+          <t>2229011</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9120,12 +9120,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>30,14%</t>
+          <t>30,12%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>32,47%</t>
+          <t>32,39%</t>
         </is>
       </c>
     </row>
@@ -9148,12 +9148,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>56650</t>
+          <t>57082</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>92760</t>
+          <t>94635</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9163,12 +9163,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9183,12 +9183,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>65542</t>
+          <t>65716</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>104974</t>
+          <t>102850</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9198,12 +9198,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9218,12 +9218,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>132885</t>
+          <t>135235</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>186331</t>
+          <t>184653</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9233,12 +9233,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,68%</t>
         </is>
       </c>
     </row>
